--- a/data/members_template.xlsx
+++ b/data/members_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PlayGround\birthdaycard\birtdaygreeting\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD9EF7D8-BA2D-4263-B93D-AA55796B9E22}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0143E0E6-D46B-4657-ABD5-9CADEB859CE9}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -64,9 +64,6 @@
     <t>Resume URL</t>
   </si>
   <si>
-    <t>Date Join TMA</t>
-  </si>
-  <si>
     <t>Date Of Birth</t>
   </si>
   <si>
@@ -137,6 +134,9 @@
   </si>
   <si>
     <t>ABC</t>
+  </si>
+  <si>
+    <t>Date Join</t>
   </si>
 </sst>
 </file>
@@ -538,84 +538,84 @@
         <v>13</v>
       </c>
       <c r="O1" t="s">
+        <v>38</v>
+      </c>
+      <c r="P1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" t="s">
+      <c r="V1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" t="s">
+      <c r="W1" t="s">
         <v>21</v>
       </c>
-      <c r="W1" t="s">
+      <c r="X1" t="s">
         <v>22</v>
-      </c>
-      <c r="X1" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" t="s">
         <v>24</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D2" t="s">
         <v>25</v>
       </c>
-      <c r="C2" t="s">
+      <c r="E2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>34</v>
-      </c>
-      <c r="D2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E2" t="s">
-        <v>27</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>35</v>
       </c>
       <c r="G2">
         <v>1231</v>
       </c>
       <c r="H2" t="s">
+        <v>35</v>
+      </c>
+      <c r="I2" t="s">
+        <v>27</v>
+      </c>
+      <c r="J2" t="s">
         <v>36</v>
       </c>
-      <c r="I2" t="s">
+      <c r="K2" t="s">
+        <v>37</v>
+      </c>
+      <c r="O2" t="s">
         <v>28</v>
       </c>
-      <c r="J2" t="s">
-        <v>37</v>
-      </c>
-      <c r="K2" t="s">
-        <v>38</v>
-      </c>
-      <c r="O2" t="s">
+      <c r="P2" t="s">
         <v>29</v>
       </c>
-      <c r="P2" t="s">
+      <c r="S2" t="s">
         <v>30</v>
       </c>
-      <c r="S2" t="s">
+      <c r="T2" t="s">
         <v>31</v>
       </c>
-      <c r="T2" t="s">
+      <c r="V2" t="s">
         <v>32</v>
-      </c>
-      <c r="V2" t="s">
-        <v>33</v>
       </c>
     </row>
   </sheetData>
